--- a/resources/BookList.xlsx
+++ b/resources/BookList.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/resources/BookList.xlsx
+++ b/resources/BookList.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Projects\Github\Java-Maven-Practice\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF901AC-BAC7-456A-9E75-83C20AF04D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4DD6C3-6CCD-4FE6-B645-AF3754C00C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{F0696337-5D3C-427A-BA5D-5408D2E217DA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{F0696337-5D3C-427A-BA5D-5408D2E217DA}"/>
   </bookViews>
   <sheets>
     <sheet name="30-Jun-2025" sheetId="15" r:id="rId1"/>
     <sheet name="06-Jul-2025" sheetId="16" r:id="rId2"/>
     <sheet name="26-Oct-2025" sheetId="17" r:id="rId3"/>
-    <sheet name="Books to buy" sheetId="14" r:id="rId4"/>
+    <sheet name="01-May-2026" sheetId="18" r:id="rId4"/>
+    <sheet name="Books to buy" sheetId="14" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4880" uniqueCount="2166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6682" uniqueCount="2418">
   <si>
     <t>1</t>
   </si>
@@ -6535,6 +6536,762 @@
   </si>
   <si>
     <t>Minute Difference: 34 minute(s)</t>
+  </si>
+  <si>
+    <t>Digital Minimalism: Choosing A Focused Life in A Noisy World</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/0241737990/?coliid=I287LZTLT8JN1Q&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>SO GOOD THEY CAN'T IGNORE YOU</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/0349420211/?coliid=I1APQPFA4ORTH6&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Grit: Why passion and resilience are the secrets to success</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/1785040200/?coliid=I1IIE527R7PMM5&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>The Diving Bell and the Butterfly</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/0375701214/?coliid=I257MEMHXQ42YM&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 804</t>
+  </si>
+  <si>
+    <t>Think on these things</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8187326840/?coliid=I1IUN98B86MAYD&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Practice of Brahmacharya</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8170520673/?coliid=I39F88YX6W25XA&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Iconoclast: A Reflective Biography of Dr Babasaheb Ambedkar</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/0670093882/?coliid=I1I0RFUMFQU5RE&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 869</t>
+  </si>
+  <si>
+    <t>PREM RAS SIDDHANT - HINDI</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8194238641/?coliid=I26W2ERHK19ZGL&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Śrī Bhaktamāl With Bhaktisabodhini Ṭīkā by Śrī Priyādāsajī |Language: Hindi |Size: Large (ग्रन्थाकार) |Code: 2066</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0BGX3MSQB/?coliid=I3CMDNNUG80LX6&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Bhakti Shatak - Hindi (With Meaning)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/9380661266/?coliid=I1WKNFYWF1N041&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Radha Govind Geet- Vol-1 &amp; Vol-2</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8190966162/?coliid=I21R12FI8TJD6I&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 995</t>
+  </si>
+  <si>
+    <t>SAYAJIRAO GAEKWAD III (PB)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/9353337925/?coliid=ILJW5YNO0U3FH&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>SAYAJI RAO GAEKWAD III</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/9354912044/?coliid=I39406P9AF6HCD&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Dr. Mrunal Patel's Economy for UPSC Civil Services Examination and All Other Competitive Exams (PCB 13) (PCB 12 Book + PCB 13 Updates Booklet) | Set ... JPSC, UPPSC, TNPSC, UGC NET, NBARD, SEBI</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/9390997089/?coliid=ITZS39OREG8DQ&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 986</t>
+  </si>
+  <si>
+    <t>Rashmirathi : Dinkar Granthmala</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8180313638/?coliid=I3V8TP9HUPCRU7&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Yog Vashishth (Sankshipt) (Gita Press, Gorakhpur) / Yog Vashist / YogVashist / Yog Vashista</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0BGXFV2S2/?coliid=I281GH585W8XBJ&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 306</t>
+  </si>
+  <si>
+    <t>The Difficulty of Being Good</t>
+  </si>
+  <si>
+    <t>₹ 361</t>
+  </si>
+  <si>
+    <t>₹ 674</t>
+  </si>
+  <si>
+    <t>The Mahabharata</t>
+  </si>
+  <si>
+    <t>₹ 596</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8172764820/?coliid=INOYJ824ZABX6&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Mahabharata - Vol. 1 &amp; 2</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8129114925/?coliid=I3D0988MXKR4CD&amp;colid=H15GSZNFJH64&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 271</t>
+  </si>
+  <si>
+    <t>The Culture Code: The Secrets of Highly Successful Groups</t>
+  </si>
+  <si>
+    <t>Meditations (PREMIUM PAPERBACK, PENGUIN INDIA)</t>
+  </si>
+  <si>
+    <t>₹ 1360</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/0944002048/?coliid=I1W9JF4HBQGZ1&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Think and Grow Rich: The Landmark Bestseller Now Revised and Updated for the 21st Century</t>
+  </si>
+  <si>
+    <t>Kumarasambhavam: The Origin Of The Young God</t>
+  </si>
+  <si>
+    <t>Ashtavakra Gita by Acharya Prashant</t>
+  </si>
+  <si>
+    <t>The Illustrated Ramayana: The timeless epic of duty, love, and redemption</t>
+  </si>
+  <si>
+    <t>₹ 1159</t>
+  </si>
+  <si>
+    <t>₹ 1434</t>
+  </si>
+  <si>
+    <t>Bhagavad Gita (Vol 1 &amp; Vol 2) by Acharya Prashant</t>
+  </si>
+  <si>
+    <t>₹ 51</t>
+  </si>
+  <si>
+    <t>Philosophy: Who Needs It</t>
+  </si>
+  <si>
+    <t>₹ 303</t>
+  </si>
+  <si>
+    <t>Good Vibes, Good Life: How Self-love Is</t>
+  </si>
+  <si>
+    <t>GODAN (PREMCHAND) [Hardcover]</t>
+  </si>
+  <si>
+    <t>The Fountainhead</t>
+  </si>
+  <si>
+    <t>The Naga Warriors 1: Battle of Gokul Vol 1</t>
+  </si>
+  <si>
+    <t>History of the Russian Revolution</t>
+  </si>
+  <si>
+    <t>₹ 693</t>
+  </si>
+  <si>
+    <t>₹ 416</t>
+  </si>
+  <si>
+    <t>₹ 2001</t>
+  </si>
+  <si>
+    <t>₹ 1682</t>
+  </si>
+  <si>
+    <t>₹ 1275</t>
+  </si>
+  <si>
+    <t>₹ 1999</t>
+  </si>
+  <si>
+    <t>Team of Rivals: The Political Genius of Abraham Lincoln</t>
+  </si>
+  <si>
+    <t>₹ 676</t>
+  </si>
+  <si>
+    <t>Bihar Diaries: The True Story of How Bihar's Most Dangerous Criminal Was Caught | A popular show on Netflix, named Khakee</t>
+  </si>
+  <si>
+    <t>The Day of the Triffids</t>
+  </si>
+  <si>
+    <t>₹ 787</t>
+  </si>
+  <si>
+    <t>₹ 941</t>
+  </si>
+  <si>
+    <t>₹ 2762</t>
+  </si>
+  <si>
+    <t>₹ 2172</t>
+  </si>
+  <si>
+    <t>₹ 1718</t>
+  </si>
+  <si>
+    <t>Chitramay Sri Durga Saptashati (Including Shipping Cost) [Hardcover] Gita Press Gorakhpur [Hardcover] Gita Press Gorakhpur [Hardcover] Gita Press Gorakhpur: Hindi</t>
+  </si>
+  <si>
+    <t>Norwegian Wood: Discover Haruki Murakami’s most beloved novel</t>
+  </si>
+  <si>
+    <t>₹ 587</t>
+  </si>
+  <si>
+    <t>₹ 562</t>
+  </si>
+  <si>
+    <t>Frontiers: The Relentless Battles Between Shivaji and Aurangzeb | Epic War of Marathas vs Mughals |Indian History, Warfare &amp; Political Strategy</t>
+  </si>
+  <si>
+    <t>Challenging Destiny: A Biography of Chhatrapati Shivaji [English]</t>
+  </si>
+  <si>
+    <t>₹ 595</t>
+  </si>
+  <si>
+    <t>The Life and Death of Sambhaji: A Powerful Account of the Fearless Maratha Warrior &amp; His Battle Against Aurangzeb | Chhava’s Real Legacy</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8122501028/?coliid=I2TQC4P8MF4UAU&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>The Valmiki Ramayana Vol. 3</t>
+  </si>
+  <si>
+    <t>The Valmiki Ramayana Vol. 2</t>
+  </si>
+  <si>
+    <t>The Valmiki Ramayana Vol. 1</t>
+  </si>
+  <si>
+    <t>You Can Heal Your Life Hay, Louise L.</t>
+  </si>
+  <si>
+    <t>₹ 331</t>
+  </si>
+  <si>
+    <t>'What Do You Care What Other People Think?': Further Adventures of a Curious Character</t>
+  </si>
+  <si>
+    <t>₹ 3071</t>
+  </si>
+  <si>
+    <t>₹ 1045</t>
+  </si>
+  <si>
+    <t>₹ 310</t>
+  </si>
+  <si>
+    <t>₹ 302</t>
+  </si>
+  <si>
+    <t>Last Mughal</t>
+  </si>
+  <si>
+    <t>₹ 405</t>
+  </si>
+  <si>
+    <t>Sanskar | संस्कार</t>
+  </si>
+  <si>
+    <t>₹ 179</t>
+  </si>
+  <si>
+    <t>₹ 1600</t>
+  </si>
+  <si>
+    <t>₹ 748</t>
+  </si>
+  <si>
+    <t>₹ 683</t>
+  </si>
+  <si>
+    <t>The Babri Masjid 1528 Question 2003: A Matter Of National Honour</t>
+  </si>
+  <si>
+    <t>₹ 578</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/8119660056/?coliid=I2EWUPDZZ7QP9D&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 12028</t>
+  </si>
+  <si>
+    <t>White Nights by Fyodor Dostoyevsky: A Timeless Story of Love, Longing &amp; Solitude | Classic Fiction, Russian Literature, Romantic Novella | Penguin Little Black Classics</t>
+  </si>
+  <si>
+    <t>₹ 126</t>
+  </si>
+  <si>
+    <t>₹ 12999</t>
+  </si>
+  <si>
+    <t>₹ 518</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/9357051481/?coliid=I2DH9UE4EUZGFT&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>Congress Radio: Usha Mehta and the Underground Radio Station of 1942</t>
+  </si>
+  <si>
+    <t>Indira Gandhi - Tryst with Power</t>
+  </si>
+  <si>
+    <t>Glimpses Of World History</t>
+  </si>
+  <si>
+    <t>₹ 384</t>
+  </si>
+  <si>
+    <t>Letters from a Father to His Daughter</t>
+  </si>
+  <si>
+    <t>The Emergency</t>
+  </si>
+  <si>
+    <t>₹ 406</t>
+  </si>
+  <si>
+    <t>₹ 770</t>
+  </si>
+  <si>
+    <t>₹ 829</t>
+  </si>
+  <si>
+    <t>₹ 1978</t>
+  </si>
+  <si>
+    <t>A Hundred Measures Of Time: Tiruviruttam</t>
+  </si>
+  <si>
+    <t>Endless Song</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/9353024951/?coliid=I236ATP2ZAPW2C&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 653</t>
+  </si>
+  <si>
+    <t>₹ 628</t>
+  </si>
+  <si>
+    <t>Keeping the Jewel in the Crown: The British Betrayal of India</t>
+  </si>
+  <si>
+    <t>₹ 1339</t>
+  </si>
+  <si>
+    <t>Somadeva: Tales from the Kathasaritsagara</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/0140247211/?coliid=I2QX344CJ2LA1T&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 188</t>
+  </si>
+  <si>
+    <t>Kadambari</t>
+  </si>
+  <si>
+    <t>The Clay Toy-Cart: Mrchchakatikam</t>
+  </si>
+  <si>
+    <t>₹ 328</t>
+  </si>
+  <si>
+    <t>Varaha Mihira's Brihat Jataka</t>
+  </si>
+  <si>
+    <t>₹ 895</t>
+  </si>
+  <si>
+    <t>₹ 410</t>
+  </si>
+  <si>
+    <t>Abhijnanashakuntalam (HB)</t>
+  </si>
+  <si>
+    <t>₹ 605</t>
+  </si>
+  <si>
+    <t>Malavikagnimitram: The Dancer And The King</t>
+  </si>
+  <si>
+    <t>The Desert Fathers: Sayings of the Early Christian Monks</t>
+  </si>
+  <si>
+    <t>₹ 344</t>
+  </si>
+  <si>
+    <t>Early Christian Writings: The Apostolic Fathers</t>
+  </si>
+  <si>
+    <t>Genghis Khan and the Making of the Modern World</t>
+  </si>
+  <si>
+    <t>₹ 525</t>
+  </si>
+  <si>
+    <t>₹ 535</t>
+  </si>
+  <si>
+    <t>The Tibetan Book of the Dead: First Complete Translation</t>
+  </si>
+  <si>
+    <t>₹ 520</t>
+  </si>
+  <si>
+    <t>The Egyptian Book of the Dead</t>
+  </si>
+  <si>
+    <t>₹ 649</t>
+  </si>
+  <si>
+    <t>The Last Days of Socrates</t>
+  </si>
+  <si>
+    <t>₹ 481</t>
+  </si>
+  <si>
+    <t>Rome and the Mediterranean</t>
+  </si>
+  <si>
+    <t>₹ 1879</t>
+  </si>
+  <si>
+    <t>The War with Hannibal: The History of Rome from its Foundation Books 21-30</t>
+  </si>
+  <si>
+    <t>₹ 1468</t>
+  </si>
+  <si>
+    <t>The Rise of the Roman Empire</t>
+  </si>
+  <si>
+    <t>₹ 655</t>
+  </si>
+  <si>
+    <t>The Canterbury Tales</t>
+  </si>
+  <si>
+    <t>The History of the Kings of Britain</t>
+  </si>
+  <si>
+    <t>The Campaigns of Alexander</t>
+  </si>
+  <si>
+    <t>The Republic</t>
+  </si>
+  <si>
+    <t>Penguin Select Classics: Crime And Punishment: (Original, Unabridged Classic, Premium Hardbound Collector's Edition, Ideal for Gifting)</t>
+  </si>
+  <si>
+    <t>₹ 173</t>
+  </si>
+  <si>
+    <t>₹ 1407</t>
+  </si>
+  <si>
+    <t>The Ramcharitmanas 1</t>
+  </si>
+  <si>
+    <t>₹ 527</t>
+  </si>
+  <si>
+    <t>Chanakya Niti: Verses on Life and Living</t>
+  </si>
+  <si>
+    <t>₹ 191</t>
+  </si>
+  <si>
+    <t>The Courtesan's Keeper: Samaya Matrika</t>
+  </si>
+  <si>
+    <t>The Absent Traveller: Prakrit Love Poetry From The Gathasaptasati Of Satavahana Hala</t>
+  </si>
+  <si>
+    <t>₹ 695</t>
+  </si>
+  <si>
+    <t>₹ 980</t>
+  </si>
+  <si>
+    <t>₹ 550</t>
+  </si>
+  <si>
+    <t>₹ 465</t>
+  </si>
+  <si>
+    <t>A Feast of Vultures: The Hidden Business of Democracy in India</t>
+  </si>
+  <si>
+    <t>Everything You Ever Wanted to Know about Bureaucracy But Were Afraid to Ask</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/0670097195/?coliid=I2EB07LYFDMAKG&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 285</t>
+  </si>
+  <si>
+    <t>₹ 239</t>
+  </si>
+  <si>
+    <t>₹ 258</t>
+  </si>
+  <si>
+    <t>Winning in the Digital Age: Seven Building Blocks of Successful Digital Transformation</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/9386228785/?coliid=I1OHHX9F2YSK2L&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>1984 by George Orwell | A Timeless Tale of Surveillance, Power &amp; Rebellion | Classic Literature Bestseller | Must-Read Dystopian Fiction | Originial Premium Paperback Edition</t>
+  </si>
+  <si>
+    <t>₹ 1395</t>
+  </si>
+  <si>
+    <t>₹ 3422</t>
+  </si>
+  <si>
+    <t>₹ 9456</t>
+  </si>
+  <si>
+    <t>Skin in the Game: Hidden Asymmetries in Daily Life</t>
+  </si>
+  <si>
+    <t>Fooled by Randomness: The Hidden Role of Chance in Life and in the Markets</t>
+  </si>
+  <si>
+    <t>Ratan Tata: Visionary Industrialist Who Built the Tata Empire | Inspiring Biography of Leadership, Ethics &amp; Nation-Building — Complete Biography</t>
+  </si>
+  <si>
+    <t>Karmayogi: A Biography of E. Sreedharan</t>
+  </si>
+  <si>
+    <t>₹ 134</t>
+  </si>
+  <si>
+    <t>The Black Economy In India</t>
+  </si>
+  <si>
+    <t>₹ 297</t>
+  </si>
+  <si>
+    <t>₹ 2029</t>
+  </si>
+  <si>
+    <t>₹ 677</t>
+  </si>
+  <si>
+    <t>₹ 1242</t>
+  </si>
+  <si>
+    <t>₹ 2452</t>
+  </si>
+  <si>
+    <t>The Laws of Manu</t>
+  </si>
+  <si>
+    <t>The Upanishads</t>
+  </si>
+  <si>
+    <t>₹ 282</t>
+  </si>
+  <si>
+    <t>₹ 823</t>
+  </si>
+  <si>
+    <t>Ishadi Nau Upanishad – The Nine Principal Upanishads with Sanskrit Text and Hindi Commentary |Language: Hindi |Size: Medium (पुस्तकाकार) |Code: 66</t>
+  </si>
+  <si>
+    <t>₹ 205</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/0691245770/?coliid=I2UV11Q8LDC24Y&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>₹ 1328</t>
+  </si>
+  <si>
+    <t>₹ 1343</t>
+  </si>
+  <si>
+    <t>₹ 720</t>
+  </si>
+  <si>
+    <t>I'm Ok, You're Ok: A Practical Approach to Human Psychology</t>
+  </si>
+  <si>
+    <t>As a Man Thinketh – James Allen | The Classic Guide to Mindset, Motivation &amp; Success | Transform Your Life Through the Power of Thought | Premium Self-Help &amp; Philosophy Book | Original Premium Paperback Complete Edition</t>
+  </si>
+  <si>
+    <t>Meditations by Marcus Aurelius | Ancient Wisdom on Purpose, Calm &amp; Personal Growth | Philosophy, Stoicism &amp; Self-Mastery | A Stoic Classic for Mental Strength &amp; Inner Clarity | Wisdom for Modern Living | Original Premium Paperback Edition | Best Seller</t>
+  </si>
+  <si>
+    <t>The Story of My Experiments With Truth by Mahatma Gandhi I Books on Non Violence and Truth I Inspirational Biographies I Indian History Freedom Movement I Premium Original Paperback Edition</t>
+  </si>
+  <si>
+    <t>Black Holes: The Reith Lectures</t>
+  </si>
+  <si>
+    <t>₹ 544</t>
+  </si>
+  <si>
+    <t>₹ 918</t>
+  </si>
+  <si>
+    <t>₹ 462</t>
+  </si>
+  <si>
+    <t>₹ 1709</t>
+  </si>
+  <si>
+    <t>Lokvadi Tulsidas | लोकवादी तुलसीदास</t>
+  </si>
+  <si>
+    <t>₹ 604</t>
+  </si>
+  <si>
+    <t>Kitne Ghazi Aaye, Kitne Ghazi Gaye: A True Life Account of Bravery And Sacrifice of An Army Soldier Who Served India For More Than 40 Years.</t>
+  </si>
+  <si>
+    <t>₹ 553</t>
+  </si>
+  <si>
+    <t>₹ 1959</t>
+  </si>
+  <si>
+    <t>₹ 162</t>
+  </si>
+  <si>
+    <t>₹ 994</t>
+  </si>
+  <si>
+    <t>₹ 848</t>
+  </si>
+  <si>
+    <t>₹ 2701</t>
+  </si>
+  <si>
+    <t>Masala Lab: The Science of Indian Cooking - the bestseller on food, the definitive book for every Indian kitchen, illustrated</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>₹ 1264</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>441</t>
+  </si>
+  <si>
+    <t>Let's Build A Company: A Start-up Story Minus the Bullshit</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>₹ 8911</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>₹ 1524</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/1732380325/?coliid=I17EY1P3Y4YAJ5&amp;colid=H15GSZNFJH64&amp;psc=0&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>₹ 885</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>Total Price: ₹261929</t>
+  </si>
+  <si>
+    <t>Minute Difference: 36 minute(s)</t>
   </si>
 </sst>
 </file>
@@ -24944,6 +25701,6331 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D454"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="41.33203125" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>2185</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>2282</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>2347</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D403" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D405" s="2" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D407" s="2" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D409" s="2" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D410" s="2" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C413" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D413" s="2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D414" s="2" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415" s="2" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C415" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A416" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A419" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A420" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C420" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422" s="2" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424" s="2" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D424" s="2" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D426" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429" s="2" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430" s="2" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A433" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D433" s="2" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A434" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A435" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A436" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D436" s="2" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437" s="2" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C437" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A438" s="2" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A439" s="2" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C439" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A440" s="2" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D440" s="2" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A441" s="2" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A442" s="2" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A443" s="2" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A444" s="2" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445" s="2" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A446" s="2" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C446" s="2" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A447" s="2" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C447" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A448" s="2" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449" s="2" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C449" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450" s="2" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C450" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B453" s="1" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B454" s="1" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB219F3B-2DCF-4CCF-9077-3FCC135F4E24}">
   <dimension ref="A1:C183"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/resources/BookList.xlsx
+++ b/resources/BookList.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Projects\Github\Java-Maven-Practice\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Projects\Java-Maven-Practice\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4DD6C3-6CCD-4FE6-B645-AF3754C00C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
